--- a/mlef_pipeline/results/DCR/SQUAMOUS/RWD_DP_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/RWD_DP_PYRAD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.75 ± 0.14</t>
+          <t>0.74 ± 0.14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.68 ± 0.16</t>
+          <t>0.66 ± 0.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71 ± 0.25</t>
+          <t>0.71 ± 0.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.72 ± 0.27</t>
+          <t>0.62 ± 0.18</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.50 ± 0.39</t>
+          <t>0.44 ± 0.38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.48 ± 0.45</t>
+          <t>0.56 ± 0.43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
